--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260824.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260824.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,366,000</t>
+          <t>615,600</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>615,600</t>
+          <t>1,366,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>5,840,000</t>
+          <t>3,289,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,289,000</t>
+          <t>5,840,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,221,441</t>
+          <t>956,659</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>956,659</t>
+          <t>1,221,441</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,407,384</t>
+          <t>2,651,703</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>2,651,703</t>
+          <t>1,407,384</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>594,000</t>
+          <t>10,821,121</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>594,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>10,821,121</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,210,076</t>
+          <t>821,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>202609WVHFU6F</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1,210,076</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>202609WVHFU6F</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>821,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>5,063,956</t>
+          <t>185,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>185,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>5,063,956</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,794,000</t>
+          <t>117,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>117,000</t>
+          <t>1,794,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>259,000</t>
+          <t>160,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>160,000</t>
+          <t>694,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>694,000</t>
+          <t>259,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
